--- a/preorder_forms/039_pre_order_form--preorder_forms.xlsx
+++ b/preorder_forms/039_pre_order_form--preorder_forms.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="settings" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -427,13 +427,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
     <col width="21" customWidth="1" min="2" max="2"/>
     <col width="21" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="38" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -518,7 +518,11 @@
           <t>First Name</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Your first name</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
           <t>no</t>
@@ -541,7 +545,11 @@
           <t>Last Name</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Your last name</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
           <t>no</t>
@@ -564,7 +572,11 @@
           <t>Email</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Your email address</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
           <t>no</t>
@@ -587,7 +599,11 @@
           <t>Phone</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Your phone number</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
           <t>no</t>
@@ -610,7 +626,11 @@
           <t>Preorder Message</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Any special instructions or comments</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
           <t>no</t>
@@ -633,7 +653,11 @@
           <t>Preorder Date</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Date of pre-order</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
           <t>no</t>
@@ -656,7 +680,11 @@
           <t>Preorder Time</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Time of pre-order</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
           <t>no</t>
@@ -679,7 +707,11 @@
           <t>Product Name</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Name of product</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
           <t>no</t>
@@ -702,7 +734,11 @@
           <t>Product Description</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Description of product</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
           <t>no</t>
@@ -725,7 +761,11 @@
           <t>Order ID</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Unique order ID</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
           <t>no</t>
@@ -748,7 +788,11 @@
           <t>Preorder Note</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Any additional notes</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
           <t>no</t>
@@ -758,20 +802,24 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>first_name</t>
+          <t>date</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>First Name</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Date of pre-order</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
           <t>no</t>
@@ -781,297 +829,25 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>time</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>last_name</t>
+          <t>time</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Last Name</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
+          <t>Time</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Time of pre-order</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>email</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Email</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>phone</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Phone</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>product_name</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Product Name</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>product_description</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Product Description</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>order_id</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Order ID</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>preorder_note</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Preorder Note</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Time</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>first_name</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>First Name</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>last_name</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Last Name</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>email</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Email</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>phone</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Phone</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
